--- a/범운해운항공_전체데이터_통합백업_2026-10-24 (1).xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-24 (1).xlsx
@@ -12,7 +12,10 @@
     <sheet name="경비_지출내역" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="거래처미팅노트" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="업무용일지" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="시스템설정" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="고객사계정" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="고객화물접수" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="고객수정이력" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="시스템설정" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9804,7 +9807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10194,6 +10197,36 @@
         </is>
       </c>
       <c r="F13" t="inlineStr">
+        <is>
+          <t>미지급</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>109900</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>탑 이동훈 이사 저녁식대</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>미지급</t>
         </is>
@@ -10522,20 +10555,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>__SYSTEM_META__</t>
+          <t>SYSTEM_META</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "지급상태": "미지급", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [], "customer_requests": [], "customer_history": []}</t>
         </is>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-24 (1).xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-24 (1).xlsx
@@ -9807,7 +9807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10227,6 +10227,36 @@
         </is>
       </c>
       <c r="F14" t="inlineStr">
+        <is>
+          <t>미지급</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>주유비(차량유지비)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>125000</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>엔진오일 교환비용 5710</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>미지급</t>
         </is>
@@ -10607,7 +10637,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "지급상태": "미지급", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [], "customer_requests": [], "customer_history": []}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "지급상태": "미지급", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [], "customer_requests": [], "customer_history": []}</t>
         </is>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-24 (1).xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-24 (1).xlsx
@@ -10585,9 +10585,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>아이디</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>비밀번호해시</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>고객사상호</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>담당자연락처</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>생성일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>joeun</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>조철희</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>승인</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-24 03:34:34</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10637,7 +10702,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "지급상태": "미지급", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [], "customer_requests": [], "customer_history": []}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [], "customer_history": []}</t>
         </is>
       </c>
     </row>
